--- a/domains_variables_and_categories.xlsx
+++ b/domains_variables_and_categories.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://southwestacademichealthscie-my.sharepoint.com/personal/richard_blackwell_healthinnovationsouthwest_com/Documents/Workspace/testbed/ipf_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://southwestacademichealthscie-my.sharepoint.com/personal/richard_blackwell_healthinnovationsouthwest_com/Documents/Workspace/intersectionality_using_ipf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{B8BD4DE0-24E8-4EA3-B818-CA9B90F70F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA3DFCBE-E94A-42AF-B9B8-29A21944083C}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{B8BD4DE0-24E8-4EA3-B818-CA9B90F70F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5335974E-4262-4499-94D1-9CE6EE91B761}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{653C01C1-5E57-42DD-8685-397F2D8B1215}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -561,10 +561,114 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Level" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="Individual"/>
+        <s v="Household"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Categories" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="100">
+        <s v="English or Welsh"/>
+        <s v="Any other UK languages"/>
+        <s v="European languages (EU)"/>
+        <s v="Other European languages (non-EU)"/>
+        <s v="Asian languages"/>
+        <s v="Oceanic or Australian languages"/>
+        <s v="North or South American languages"/>
+        <s v="African languages"/>
+        <s v="Sign and supported languages"/>
+        <s v="Any other languages"/>
+        <s v="NA"/>
+        <s v="Main language is English (English or Welsh in Wales)"/>
+        <s v="Main language is not English (English or Welsh in Wales): Can speak English very well or well"/>
+        <s v="Main language is not English (English or Welsh in Wales): Cannot speak English well"/>
+        <s v="Main language is not English (English or Welsh in Wales): Cannot speak English"/>
+        <s v="None"/>
+        <s v="Level 1"/>
+        <s v="Level 2"/>
+        <s v="Level 3"/>
+        <s v="Level 4"/>
+        <s v="Other"/>
+        <s v="Aged 15 years and under"/>
+        <s v="Aged 16 to 24 years"/>
+        <s v="Aged 25 to 34 years"/>
+        <s v="Aged 35 to 49 years"/>
+        <s v="Aged 50 to 64 years"/>
+        <s v="Aged 65 to 74 years"/>
+        <s v="Aged 75 to 84 years"/>
+        <s v="Aged 85 years and over"/>
+        <s v="Disabled under the Equality Act"/>
+        <s v="Not disabled under the Equality Act"/>
+        <s v="Does not apply"/>
+        <s v="Very good or good health"/>
+        <s v="Fair health"/>
+        <s v="Bad or very bad health"/>
+        <s v="No cars or vans in household"/>
+        <s v="1 or more cars or vans in household"/>
+        <s v="L1, L2 and L3: Higher managerial, administrative and professional occupations"/>
+        <s v="L4, L5 and L6: Lower managerial, administrative and professional occupations"/>
+        <s v="L7: Intermediate occupations"/>
+        <s v="L8 and L9: Small employers and own account workers"/>
+        <s v="L10 and L11: Lower supervisory and technical occupations"/>
+        <s v="L12: Semi-routine occupations"/>
+        <s v="L13: Routine occupations"/>
+        <s v="L14.1 and L14.2: Never worked and long-term unemployed"/>
+        <s v="L15: Full-time students"/>
+        <s v="Owned: Owns outright"/>
+        <s v="Owned: Owns with a mortgage or loan or shared ownership"/>
+        <s v="Rented: Social rented"/>
+        <s v="Private rented or lives rent free"/>
+        <s v="1. Managers, directors and senior officials"/>
+        <s v="2. Professional occupations"/>
+        <s v="3. Associate professional and technical occupations"/>
+        <s v="4. Administrative and secretarial occupations"/>
+        <s v="5. Skilled trades occupations"/>
+        <s v="6. Caring, leisure and other service occupations"/>
+        <s v="7. Sales and customer service occupations"/>
+        <s v="8. Process, plant and machine operatives"/>
+        <s v="9. Elementary occupations"/>
+        <s v="Provides no unpaid care"/>
+        <s v="Provides 19 or less hours unpaid care a week"/>
+        <s v="Provides 20 to 49 hours unpaid care a week"/>
+        <s v="Provides 50 or more hours unpaid care a week"/>
+        <s v="One-person household: Aged 66 years and over"/>
+        <s v="One-person household: Other"/>
+        <s v="Single family household: Couple family household: No children"/>
+        <s v="Single family household: Couple family household: Dependent children"/>
+        <s v="Single family household: Couple family household: All children non-dependent"/>
+        <s v="Single family household: Lone parent household"/>
+        <s v="Other household types"/>
+        <s v="One-person household"/>
+        <s v="Married or civil partnership couple household"/>
+        <s v="Cohabiting couple household"/>
+        <s v="Lone parent household"/>
+        <s v="Multi-person household"/>
+        <s v="Economically active (excluding full-time students): In employment"/>
+        <s v="Economically active (excluding full-time students): Unemployed: Seeking work or waiting to start a job already obtained: Available to start working within 2 weeks"/>
+        <s v="Economically active and a full-time student: In employment"/>
+        <s v="Economically active and a full-time student: Unemployed: Seeking work or waiting to start a job already obtained: Available to start working within 2 weeks"/>
+        <s v="Economically inactive: Retired"/>
+        <s v="Economically inactive: Student"/>
+        <s v="Economically inactive: Looking after home or family"/>
+        <s v="Economically inactive: Long-term sick or disabled"/>
+        <s v="Economically inactive: Other"/>
+        <s v="Asian, Asian British or Asian Welsh"/>
+        <s v="Black, Black British, Black Welsh, Caribbean or African"/>
+        <s v="Mixed or Multiple ethnic groups"/>
+        <s v="White"/>
+        <s v="Other ethnic group"/>
+        <s v="No religion"/>
+        <s v="Christian"/>
+        <s v="All other religions"/>
+        <s v="Not answered"/>
+        <s v="Born in the UK"/>
+        <s v="10 years or more"/>
+        <s v="5 years or more, but less than 10 years"/>
+        <s v="2 years or more, but less than 5 years"/>
+        <s v="Less than 2 years"/>
+        <s v="Female"/>
+        <s v="Male"/>
+      </sharedItems>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -580,974 +684,974 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <s v="Individual"/>
-    <s v="English or Welsh"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Individual"/>
-    <s v="Any other UK languages"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Individual"/>
-    <s v="European languages (EU)"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Individual"/>
-    <s v="Other European languages (non-EU)"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Individual"/>
-    <s v="Asian languages"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Individual"/>
-    <s v="Oceanic or Australian languages"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Individual"/>
-    <s v="North or South American languages"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Individual"/>
-    <s v="African languages"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Individual"/>
-    <s v="Sign and supported languages"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Individual"/>
-    <s v="Any other languages"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Individual"/>
-    <s v="NA"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="Individual"/>
-    <s v="Main language is English (English or Welsh in Wales)"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="Individual"/>
-    <s v="Main language is not English (English or Welsh in Wales): Can speak English very well or well"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="Individual"/>
-    <s v="Main language is not English (English or Welsh in Wales): Cannot speak English well"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="Individual"/>
-    <s v="Main language is not English (English or Welsh in Wales): Cannot speak English"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="Individual"/>
-    <s v="NA"/>
-  </r>
-  <r>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="None"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="10"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="Level 1"/>
+    <x v="0"/>
+    <x v="15"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="Level 2"/>
+    <x v="0"/>
+    <x v="16"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="Level 3"/>
+    <x v="0"/>
+    <x v="17"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="Level 4"/>
+    <x v="0"/>
+    <x v="18"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="Other"/>
+    <x v="0"/>
+    <x v="19"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="NA"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 15 years and under"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 16 to 24 years"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 25 to 34 years"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 35 to 49 years"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 50 to 64 years"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 65 to 74 years"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 75 to 84 years"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 85 years and over"/>
+    <x v="0"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="28"/>
   </r>
   <r>
     <x v="1"/>
     <x v="4"/>
-    <s v="Individual"/>
-    <s v="Disabled under the Equality Act"/>
+    <x v="0"/>
+    <x v="29"/>
   </r>
   <r>
     <x v="1"/>
     <x v="4"/>
-    <s v="Individual"/>
-    <s v="Not disabled under the Equality Act"/>
+    <x v="0"/>
+    <x v="30"/>
   </r>
   <r>
     <x v="1"/>
     <x v="4"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="1"/>
     <x v="5"/>
-    <s v="Individual"/>
-    <s v="Very good or good health"/>
+    <x v="0"/>
+    <x v="32"/>
   </r>
   <r>
     <x v="1"/>
     <x v="5"/>
-    <s v="Individual"/>
-    <s v="Fair health"/>
+    <x v="0"/>
+    <x v="33"/>
   </r>
   <r>
     <x v="1"/>
     <x v="5"/>
-    <s v="Individual"/>
-    <s v="Bad or very bad health"/>
+    <x v="0"/>
+    <x v="34"/>
   </r>
   <r>
     <x v="1"/>
     <x v="5"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="1"/>
     <x v="6"/>
-    <s v="Household"/>
-    <s v="No cars or vans in household"/>
+    <x v="1"/>
+    <x v="35"/>
   </r>
   <r>
     <x v="1"/>
     <x v="6"/>
-    <s v="Household"/>
-    <s v="1 or more cars or vans in household"/>
+    <x v="1"/>
+    <x v="36"/>
   </r>
   <r>
     <x v="1"/>
     <x v="6"/>
-    <s v="Household"/>
-    <s v="Does not apply"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 15 years and under"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 16 to 24 years"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 25 to 34 years"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 35 to 49 years"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 50 to 64 years"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 65 to 74 years"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 75 to 84 years"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 85 years and over"/>
+    <x v="1"/>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="28"/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <s v="Individual"/>
-    <s v="L1, L2 and L3: Higher managerial, administrative and professional occupations"/>
+    <x v="0"/>
+    <x v="37"/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <s v="Individual"/>
-    <s v="L4, L5 and L6: Lower managerial, administrative and professional occupations"/>
+    <x v="0"/>
+    <x v="38"/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <s v="Individual"/>
-    <s v="L7: Intermediate occupations"/>
+    <x v="0"/>
+    <x v="39"/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <s v="Individual"/>
-    <s v="L8 and L9: Small employers and own account workers"/>
+    <x v="0"/>
+    <x v="40"/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <s v="Individual"/>
-    <s v="L10 and L11: Lower supervisory and technical occupations"/>
+    <x v="0"/>
+    <x v="41"/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <s v="Individual"/>
-    <s v="L12: Semi-routine occupations"/>
+    <x v="0"/>
+    <x v="42"/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <s v="Individual"/>
-    <s v="L13: Routine occupations"/>
+    <x v="0"/>
+    <x v="43"/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <s v="Individual"/>
-    <s v="L14.1 and L14.2: Never worked and long-term unemployed"/>
+    <x v="0"/>
+    <x v="44"/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <s v="Individual"/>
-    <s v="L15: Full-time students"/>
+    <x v="0"/>
+    <x v="45"/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="None"/>
+    <x v="0"/>
+    <x v="15"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="Level 1"/>
+    <x v="0"/>
+    <x v="16"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="Level 2"/>
+    <x v="0"/>
+    <x v="17"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="Level 3"/>
+    <x v="0"/>
+    <x v="18"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="Level 4"/>
+    <x v="0"/>
+    <x v="19"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="Other"/>
+    <x v="0"/>
+    <x v="20"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <s v="Individual"/>
-    <s v="NA"/>
+    <x v="0"/>
+    <x v="10"/>
   </r>
   <r>
     <x v="2"/>
     <x v="8"/>
-    <s v="Household"/>
-    <s v="Owned: Owns outright"/>
+    <x v="1"/>
+    <x v="46"/>
   </r>
   <r>
     <x v="2"/>
     <x v="8"/>
-    <s v="Household"/>
-    <s v="Owned: Owns with a mortgage or loan or shared ownership"/>
+    <x v="1"/>
+    <x v="47"/>
   </r>
   <r>
     <x v="2"/>
     <x v="8"/>
-    <s v="Household"/>
-    <s v="Rented: Social rented"/>
+    <x v="1"/>
+    <x v="48"/>
   </r>
   <r>
     <x v="2"/>
     <x v="8"/>
-    <s v="Household"/>
-    <s v="Private rented or lives rent free"/>
+    <x v="1"/>
+    <x v="49"/>
   </r>
   <r>
     <x v="2"/>
     <x v="8"/>
-    <s v="Household"/>
-    <s v="Does not apply"/>
+    <x v="1"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="2"/>
     <x v="9"/>
-    <s v="Individual"/>
-    <s v="1. Managers, directors and senior officials"/>
+    <x v="0"/>
+    <x v="50"/>
   </r>
   <r>
     <x v="2"/>
     <x v="9"/>
-    <s v="Individual"/>
-    <s v="2. Professional occupations"/>
+    <x v="0"/>
+    <x v="51"/>
   </r>
   <r>
     <x v="2"/>
     <x v="9"/>
-    <s v="Individual"/>
-    <s v="3. Associate professional and technical occupations"/>
+    <x v="0"/>
+    <x v="52"/>
   </r>
   <r>
     <x v="2"/>
     <x v="9"/>
-    <s v="Individual"/>
-    <s v="4. Administrative and secretarial occupations"/>
+    <x v="0"/>
+    <x v="53"/>
   </r>
   <r>
     <x v="2"/>
     <x v="9"/>
-    <s v="Individual"/>
-    <s v="5. Skilled trades occupations"/>
+    <x v="0"/>
+    <x v="54"/>
   </r>
   <r>
     <x v="2"/>
     <x v="9"/>
-    <s v="Individual"/>
-    <s v="6. Caring, leisure and other service occupations"/>
+    <x v="0"/>
+    <x v="55"/>
   </r>
   <r>
     <x v="2"/>
     <x v="9"/>
-    <s v="Individual"/>
-    <s v="7. Sales and customer service occupations"/>
+    <x v="0"/>
+    <x v="56"/>
   </r>
   <r>
     <x v="2"/>
     <x v="9"/>
-    <s v="Individual"/>
-    <s v="8. Process, plant and machine operatives"/>
+    <x v="0"/>
+    <x v="57"/>
   </r>
   <r>
     <x v="2"/>
     <x v="9"/>
-    <s v="Individual"/>
-    <s v="9. Elementary occupations"/>
+    <x v="0"/>
+    <x v="58"/>
   </r>
   <r>
     <x v="2"/>
     <x v="9"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="3"/>
     <x v="10"/>
-    <s v="Individual"/>
-    <s v="Provides no unpaid care"/>
+    <x v="0"/>
+    <x v="59"/>
   </r>
   <r>
     <x v="3"/>
     <x v="10"/>
-    <s v="Individual"/>
-    <s v="Provides 19 or less hours unpaid care a week"/>
+    <x v="0"/>
+    <x v="60"/>
   </r>
   <r>
     <x v="3"/>
     <x v="10"/>
-    <s v="Individual"/>
-    <s v="Provides 20 to 49 hours unpaid care a week"/>
+    <x v="0"/>
+    <x v="61"/>
   </r>
   <r>
     <x v="3"/>
     <x v="10"/>
-    <s v="Individual"/>
-    <s v="Provides 50 or more hours unpaid care a week"/>
+    <x v="0"/>
+    <x v="62"/>
   </r>
   <r>
     <x v="3"/>
     <x v="10"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="3"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="One-person household: Aged 66 years and over"/>
+    <x v="1"/>
+    <x v="63"/>
   </r>
   <r>
     <x v="3"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="One-person household: Other"/>
+    <x v="1"/>
+    <x v="64"/>
   </r>
   <r>
     <x v="3"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Single family household: Couple family household: No children"/>
+    <x v="1"/>
+    <x v="65"/>
   </r>
   <r>
     <x v="3"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Single family household: Couple family household: Dependent children"/>
+    <x v="1"/>
+    <x v="66"/>
   </r>
   <r>
     <x v="3"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Single family household: Couple family household: All children non-dependent"/>
+    <x v="1"/>
+    <x v="67"/>
   </r>
   <r>
     <x v="3"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Single family household: Lone parent household"/>
+    <x v="1"/>
+    <x v="68"/>
   </r>
   <r>
     <x v="3"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Other household types"/>
+    <x v="1"/>
+    <x v="69"/>
   </r>
   <r>
     <x v="3"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Does not apply"/>
+    <x v="1"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="3"/>
     <x v="12"/>
-    <s v="Household"/>
-    <s v="One-person household"/>
+    <x v="1"/>
+    <x v="70"/>
   </r>
   <r>
     <x v="3"/>
     <x v="12"/>
-    <s v="Household"/>
-    <s v="Married or civil partnership couple household"/>
+    <x v="1"/>
+    <x v="71"/>
   </r>
   <r>
     <x v="3"/>
     <x v="12"/>
-    <s v="Household"/>
-    <s v="Cohabiting couple household"/>
+    <x v="1"/>
+    <x v="72"/>
   </r>
   <r>
     <x v="3"/>
     <x v="12"/>
-    <s v="Household"/>
-    <s v="Lone parent household"/>
+    <x v="1"/>
+    <x v="73"/>
   </r>
   <r>
     <x v="3"/>
     <x v="12"/>
-    <s v="Household"/>
-    <s v="Multi-person household"/>
+    <x v="1"/>
+    <x v="74"/>
   </r>
   <r>
     <x v="3"/>
     <x v="12"/>
-    <s v="Household"/>
-    <s v="Does not apply"/>
+    <x v="1"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="3"/>
     <x v="13"/>
-    <s v="Individual"/>
-    <s v="Economically active (excluding full-time students): In employment"/>
+    <x v="0"/>
+    <x v="75"/>
   </r>
   <r>
     <x v="3"/>
     <x v="13"/>
-    <s v="Individual"/>
-    <s v="Economically active (excluding full-time students): Unemployed: Seeking work or waiting to start a job already obtained: Available to start working within 2 weeks"/>
+    <x v="0"/>
+    <x v="76"/>
   </r>
   <r>
     <x v="3"/>
     <x v="13"/>
-    <s v="Individual"/>
-    <s v="Economically active and a full-time student: In employment"/>
+    <x v="0"/>
+    <x v="77"/>
   </r>
   <r>
     <x v="3"/>
     <x v="13"/>
-    <s v="Individual"/>
-    <s v="Economically active and a full-time student: Unemployed: Seeking work or waiting to start a job already obtained: Available to start working within 2 weeks"/>
+    <x v="0"/>
+    <x v="78"/>
   </r>
   <r>
     <x v="3"/>
     <x v="13"/>
-    <s v="Individual"/>
-    <s v="Economically inactive: Retired"/>
+    <x v="0"/>
+    <x v="79"/>
   </r>
   <r>
     <x v="3"/>
     <x v="13"/>
-    <s v="Individual"/>
-    <s v="Economically inactive: Student"/>
+    <x v="0"/>
+    <x v="80"/>
   </r>
   <r>
     <x v="3"/>
     <x v="13"/>
-    <s v="Individual"/>
-    <s v="Economically inactive: Looking after home or family"/>
+    <x v="0"/>
+    <x v="81"/>
   </r>
   <r>
     <x v="3"/>
     <x v="13"/>
-    <s v="Individual"/>
-    <s v="Economically inactive: Long-term sick or disabled"/>
+    <x v="0"/>
+    <x v="82"/>
   </r>
   <r>
     <x v="3"/>
     <x v="13"/>
-    <s v="Individual"/>
-    <s v="Economically inactive: Other"/>
+    <x v="0"/>
+    <x v="83"/>
   </r>
   <r>
     <x v="3"/>
     <x v="13"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="4"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="One-person household: Aged 66 years and over"/>
+    <x v="1"/>
+    <x v="63"/>
   </r>
   <r>
     <x v="4"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="One-person household: Other"/>
+    <x v="1"/>
+    <x v="64"/>
   </r>
   <r>
     <x v="4"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Single family household: Couple family household: No children"/>
+    <x v="1"/>
+    <x v="65"/>
   </r>
   <r>
     <x v="4"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Single family household: Couple family household: Dependent children"/>
+    <x v="1"/>
+    <x v="66"/>
   </r>
   <r>
     <x v="4"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Single family household: Couple family household: All children non-dependent"/>
+    <x v="1"/>
+    <x v="67"/>
   </r>
   <r>
     <x v="4"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Single family household: Lone parent household"/>
+    <x v="1"/>
+    <x v="68"/>
   </r>
   <r>
     <x v="4"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Other household types"/>
+    <x v="1"/>
+    <x v="69"/>
   </r>
   <r>
     <x v="4"/>
     <x v="11"/>
-    <s v="Household"/>
-    <s v="Does not apply"/>
+    <x v="1"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="4"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="Asian, Asian British or Asian Welsh"/>
+    <x v="0"/>
+    <x v="84"/>
   </r>
   <r>
     <x v="4"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="Black, Black British, Black Welsh, Caribbean or African"/>
+    <x v="0"/>
+    <x v="85"/>
   </r>
   <r>
     <x v="4"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="Mixed or Multiple ethnic groups"/>
+    <x v="0"/>
+    <x v="86"/>
   </r>
   <r>
     <x v="4"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="White"/>
+    <x v="0"/>
+    <x v="87"/>
   </r>
   <r>
     <x v="4"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="Other ethnic group"/>
+    <x v="0"/>
+    <x v="88"/>
   </r>
   <r>
     <x v="4"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="4"/>
     <x v="15"/>
-    <s v="Individual"/>
-    <s v="No religion"/>
+    <x v="0"/>
+    <x v="89"/>
   </r>
   <r>
     <x v="4"/>
     <x v="15"/>
-    <s v="Individual"/>
-    <s v="Christian"/>
+    <x v="0"/>
+    <x v="90"/>
   </r>
   <r>
     <x v="4"/>
     <x v="15"/>
-    <s v="Individual"/>
-    <s v="All other religions"/>
+    <x v="0"/>
+    <x v="91"/>
   </r>
   <r>
     <x v="4"/>
     <x v="15"/>
-    <s v="Individual"/>
-    <s v="Not answered"/>
+    <x v="0"/>
+    <x v="92"/>
   </r>
   <r>
     <x v="4"/>
     <x v="15"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="4"/>
     <x v="16"/>
-    <s v="Individual"/>
-    <s v="Born in the UK"/>
+    <x v="0"/>
+    <x v="93"/>
   </r>
   <r>
     <x v="4"/>
     <x v="16"/>
-    <s v="Individual"/>
-    <s v="10 years or more"/>
+    <x v="0"/>
+    <x v="94"/>
   </r>
   <r>
     <x v="4"/>
     <x v="16"/>
-    <s v="Individual"/>
-    <s v="5 years or more, but less than 10 years"/>
+    <x v="0"/>
+    <x v="95"/>
   </r>
   <r>
     <x v="4"/>
     <x v="16"/>
-    <s v="Individual"/>
-    <s v="2 years or more, but less than 5 years"/>
+    <x v="0"/>
+    <x v="96"/>
   </r>
   <r>
     <x v="4"/>
     <x v="16"/>
-    <s v="Individual"/>
-    <s v="Less than 2 years"/>
+    <x v="0"/>
+    <x v="97"/>
   </r>
   <r>
     <x v="4"/>
     <x v="16"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="4"/>
     <x v="6"/>
-    <s v="Household"/>
-    <s v="No cars or vans in household"/>
+    <x v="1"/>
+    <x v="35"/>
   </r>
   <r>
     <x v="4"/>
     <x v="6"/>
-    <s v="Household"/>
-    <s v="1 or more cars or vans in household"/>
+    <x v="1"/>
+    <x v="36"/>
   </r>
   <r>
     <x v="4"/>
     <x v="6"/>
-    <s v="Household"/>
-    <s v="Does not apply"/>
+    <x v="1"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="5"/>
     <x v="4"/>
-    <s v="Individual"/>
-    <s v="Disabled under the Equality Act"/>
+    <x v="0"/>
+    <x v="29"/>
   </r>
   <r>
     <x v="5"/>
     <x v="4"/>
-    <s v="Individual"/>
-    <s v="Not disabled under the Equality Act"/>
+    <x v="0"/>
+    <x v="30"/>
   </r>
   <r>
     <x v="5"/>
     <x v="4"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="5"/>
     <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 15 years and under"/>
+    <x v="0"/>
+    <x v="21"/>
   </r>
   <r>
     <x v="5"/>
     <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 16 to 24 years"/>
+    <x v="0"/>
+    <x v="22"/>
   </r>
   <r>
     <x v="5"/>
     <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 25 to 34 years"/>
+    <x v="0"/>
+    <x v="23"/>
   </r>
   <r>
     <x v="5"/>
     <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 35 to 49 years"/>
+    <x v="0"/>
+    <x v="24"/>
   </r>
   <r>
     <x v="5"/>
     <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 50 to 64 years"/>
+    <x v="0"/>
+    <x v="25"/>
   </r>
   <r>
     <x v="5"/>
     <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 65 to 74 years"/>
+    <x v="0"/>
+    <x v="26"/>
   </r>
   <r>
     <x v="5"/>
     <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 75 to 84 years"/>
+    <x v="0"/>
+    <x v="27"/>
   </r>
   <r>
     <x v="5"/>
     <x v="3"/>
-    <s v="Individual"/>
-    <s v="Aged 85 years and over"/>
+    <x v="0"/>
+    <x v="28"/>
   </r>
   <r>
     <x v="5"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="Asian, Asian British or Asian Welsh"/>
+    <x v="0"/>
+    <x v="84"/>
   </r>
   <r>
     <x v="5"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="Black, Black British, Black Welsh, Caribbean or African"/>
+    <x v="0"/>
+    <x v="85"/>
   </r>
   <r>
     <x v="5"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="Mixed or Multiple ethnic groups"/>
+    <x v="0"/>
+    <x v="86"/>
   </r>
   <r>
     <x v="5"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="White"/>
+    <x v="0"/>
+    <x v="87"/>
   </r>
   <r>
     <x v="5"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="Other ethnic group"/>
+    <x v="0"/>
+    <x v="88"/>
   </r>
   <r>
     <x v="5"/>
     <x v="14"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="5"/>
     <x v="17"/>
-    <s v="Individual"/>
-    <s v="Female"/>
+    <x v="0"/>
+    <x v="98"/>
   </r>
   <r>
     <x v="5"/>
     <x v="17"/>
-    <s v="Individual"/>
-    <s v="Male"/>
+    <x v="0"/>
+    <x v="99"/>
   </r>
   <r>
     <x v="5"/>
     <x v="5"/>
-    <s v="Individual"/>
-    <s v="Very good or good health"/>
+    <x v="0"/>
+    <x v="32"/>
   </r>
   <r>
     <x v="5"/>
     <x v="5"/>
-    <s v="Individual"/>
-    <s v="Fair health"/>
+    <x v="0"/>
+    <x v="33"/>
   </r>
   <r>
     <x v="5"/>
     <x v="5"/>
-    <s v="Individual"/>
-    <s v="Bad or very bad health"/>
+    <x v="0"/>
+    <x v="34"/>
   </r>
   <r>
     <x v="5"/>
     <x v="5"/>
-    <s v="Individual"/>
-    <s v="Does not apply"/>
+    <x v="0"/>
+    <x v="31"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7AFD669B-7D08-486D-90E9-3E7F2669D6E6}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7AFD669B-7D08-486D-90E9-3E7F2669D6E6}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -1584,8 +1688,118 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="101">
+        <item x="36"/>
+        <item x="50"/>
+        <item x="94"/>
+        <item x="96"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="95"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="7"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="91"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="84"/>
+        <item x="34"/>
+        <item x="85"/>
+        <item x="93"/>
+        <item x="90"/>
+        <item x="72"/>
+        <item x="29"/>
+        <item x="31"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="82"/>
+        <item x="81"/>
+        <item x="83"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="33"/>
+        <item x="98"/>
+        <item x="37"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="97"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="73"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="99"/>
+        <item x="71"/>
+        <item x="86"/>
+        <item x="74"/>
+        <item x="10"/>
+        <item x="35"/>
+        <item x="89"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="92"/>
+        <item x="30"/>
+        <item x="5"/>
+        <item x="70"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="20"/>
+        <item x="88"/>
+        <item x="3"/>
+        <item x="69"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="49"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="59"/>
+        <item x="48"/>
+        <item x="8"/>
+        <item x="67"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="68"/>
+        <item x="32"/>
+        <item x="87"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
@@ -2031,7 +2245,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
